--- a/artfynd/A 45243-2025 artfynd.xlsx
+++ b/artfynd/A 45243-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113053975</v>
+        <v>112801440</v>
       </c>
       <c r="B2" t="n">
-        <v>96277</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordtakan, Boh</t>
+          <t>Bollestad, Kungälv, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316172</v>
+        <v>316093</v>
       </c>
       <c r="R2" t="n">
-        <v>6421366</v>
+        <v>6421388</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Håkansson</t>
+          <t>Vilhelm Moran</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Håkansson</t>
+          <t>Vilhelm Moran, Amanda Gudmundson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113053973</v>
+        <v>112801455</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +797,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bollestadbergen, Boh</t>
+          <t>Bollestad, Kungälv, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316417</v>
+        <v>316092</v>
       </c>
       <c r="R3" t="n">
-        <v>6421358</v>
+        <v>6421389</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +885,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Håkansson</t>
+          <t>Vilhelm Moran</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Håkansson</t>
+          <t>Vilhelm Moran, Amanda Gudmundson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113053974</v>
+        <v>101255530</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bollestadbergen, Boh</t>
+          <t>Bollestad, Kareby, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316556</v>
+        <v>316577</v>
       </c>
       <c r="R4" t="n">
-        <v>6421403</v>
+        <v>6421049</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,15 +994,647 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mats-Ola Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats-Ola Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102207409</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bollestad, Kareby, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>316577</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6421049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fått bild granskad av fladdermuskännare, som tror det är en nordfladdermus. Men det finns förväxlingsrisk med taiga-/mustasch-/gråskimligfladdermus.  Troligtvis en årsunge.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats-Ola Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats-Ola Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112801441</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bollestad, Kungälv, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>316092</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6421388</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Vilhelm Moran</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vilhelm Moran, Amanda Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112801457</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bollestad, Kungälv, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>316092</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6421387</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Vilhelm Moran</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vilhelm Moran, Amanda Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113053973</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bollestadbergen, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>316417</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421358</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Emma Håkansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Emma Håkansson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113053974</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bollestadbergen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>316557</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6421403</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113053975</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordtakan, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>316172</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421366</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45243-2025 artfynd.xlsx
+++ b/artfynd/A 45243-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801455</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101255530</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102207409</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113053973</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113053974</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,8 +1680,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113053975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>